--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/vendor_scorecards.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/vendor_scorecards.xlsx
@@ -484,17 +484,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C3" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -526,17 +526,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -547,17 +547,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -610,17 +610,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
